--- a/Behaviour/BCIO-behaviour-hierarchy.xlsx
+++ b/Behaviour/BCIO-behaviour-hierarchy.xlsx
@@ -839,7 +839,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>characteristic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -852,7 +852,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A bodily disposition is a disposition that inheres in some extended organism. Examples are: my disposition to catch a cold when exposed to a virus, my ability to speak the English language.</t>
+          <t>A &lt;disposition&gt; that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
